--- a/Result/profitability/8222.xlsx
+++ b/Result/profitability/8222.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.79</v>
       </c>
       <c r="M2" t="n">
-        <v>0.29875</v>
+        <v>0.32625</v>
       </c>
       <c r="N2" t="n">
-        <v>21.415</v>
+        <v>22.22375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.29375</v>
+        <v>0.2925</v>
       </c>
       <c r="N3" t="n">
-        <v>21.32125</v>
+        <v>21.5825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2925</v>
+        <v>0.31</v>
       </c>
       <c r="N4" t="n">
-        <v>20.12375</v>
+        <v>20.76625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>0.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2975</v>
+        <v>0.39125</v>
       </c>
       <c r="N5" t="n">
-        <v>19.555</v>
+        <v>21.32</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1036,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>98.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.36625</v>
+        <v>0.40375</v>
       </c>
       <c r="N6" t="n">
-        <v>19.9475</v>
+        <v>21.42375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>0.345</v>
+        <v>0.35375</v>
       </c>
       <c r="N7" t="n">
-        <v>20.82875</v>
+        <v>21.42875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -8429,6 +8429,133 @@
       </c>
       <c r="AM63" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>8222</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>248</v>
+      </c>
+      <c r="D64" t="n">
+        <v>180</v>
+      </c>
+      <c r="E64" t="n">
+        <v>68</v>
+      </c>
+      <c r="F64" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="G64" t="n">
+        <v>41</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>16.59%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J64" t="n">
+        <v>38</v>
+      </c>
+      <c r="K64" t="n">
+        <v>31</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="N64" t="n">
+        <v>21.64125</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.2162162162162162</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>2.199999999999999</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.08705975464978222</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.057677902621723</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
